--- a/Team-Data/2007-08/4-9-2007-08.xlsx
+++ b/Team-Data/2007-08/4-9-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -751,10 +818,10 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ2" t="n">
         <v>20</v>
@@ -781,13 +848,13 @@
         <v>7</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS2" t="n">
         <v>19</v>
       </c>
       <c r="AT2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU2" t="n">
         <v>11</v>
@@ -796,7 +863,7 @@
         <v>24</v>
       </c>
       <c r="AW2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX2" t="n">
         <v>4</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -843,22 +910,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E3" t="n">
         <v>62</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>0.795</v>
+        <v>0.805</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J3" t="n">
         <v>76.5</v>
@@ -867,22 +934,22 @@
         <v>0.475</v>
       </c>
       <c r="L3" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M3" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.377</v>
+        <v>0.376</v>
       </c>
       <c r="O3" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="P3" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R3" t="n">
         <v>10.1</v>
@@ -891,37 +958,37 @@
         <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U3" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V3" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X3" t="n">
         <v>4.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.5</v>
+        <v>100.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -948,19 +1015,19 @@
         <v>9</v>
       </c>
       <c r="AM3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO3" t="n">
         <v>7</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>8</v>
       </c>
       <c r="AP3" t="n">
         <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
         <v>24</v>
@@ -969,10 +1036,10 @@
         <v>9</v>
       </c>
       <c r="AT3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="n">
         <v>27</v>
@@ -987,13 +1054,13 @@
         <v>17</v>
       </c>
       <c r="AZ3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -1025,37 +1092,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E4" t="n">
         <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>0.38</v>
+        <v>0.385</v>
       </c>
       <c r="H4" t="n">
         <v>48.4</v>
       </c>
       <c r="I4" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J4" t="n">
         <v>79.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L4" t="n">
         <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="O4" t="n">
         <v>18.2</v>
@@ -1076,7 +1143,7 @@
         <v>40.3</v>
       </c>
       <c r="U4" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V4" t="n">
         <v>14.7</v>
@@ -1091,16 +1158,16 @@
         <v>5.9</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="AA4" t="n">
         <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.6</v>
+        <v>-4.7</v>
       </c>
       <c r="AD4" t="n">
         <v>1</v>
@@ -1115,10 +1182,10 @@
         <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ4" t="n">
         <v>22</v>
@@ -1142,7 +1209,7 @@
         <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR4" t="n">
         <v>21</v>
@@ -1157,22 +1224,22 @@
         <v>16</v>
       </c>
       <c r="AV4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
       </c>
       <c r="AZ4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1274,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E5" t="n">
         <v>30</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>0.385</v>
+        <v>0.39</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J5" t="n">
         <v>83.7</v>
@@ -1231,28 +1298,28 @@
         <v>0.432</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="M5" t="n">
         <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.364</v>
+        <v>0.366</v>
       </c>
       <c r="O5" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P5" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R5" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S5" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="T5" t="n">
         <v>43.1</v>
@@ -1270,7 +1337,7 @@
         <v>5.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z5" t="n">
         <v>21.7</v>
@@ -1279,13 +1346,13 @@
         <v>21.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.7</v>
+        <v>96.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.4</v>
+        <v>-3</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1300,7 +1367,7 @@
         <v>13</v>
       </c>
       <c r="AI5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1321,13 +1388,13 @@
         <v>16</v>
       </c>
       <c r="AP5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
         <v>17</v>
       </c>
       <c r="AR5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS5" t="n">
         <v>18</v>
@@ -1339,10 +1406,10 @@
         <v>12</v>
       </c>
       <c r="AV5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1351,13 +1418,13 @@
         <v>29</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -1389,19 +1456,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
         <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>0.551</v>
+        <v>0.545</v>
       </c>
       <c r="H6" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I6" t="n">
         <v>36</v>
@@ -1416,19 +1483,19 @@
         <v>6.9</v>
       </c>
       <c r="M6" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N6" t="n">
         <v>0.36</v>
       </c>
       <c r="O6" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P6" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.72</v>
+        <v>0.719</v>
       </c>
       <c r="R6" t="n">
         <v>13.3</v>
@@ -1437,10 +1504,10 @@
         <v>31.2</v>
       </c>
       <c r="T6" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="U6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V6" t="n">
         <v>14</v>
@@ -1449,7 +1516,7 @@
         <v>7.1</v>
       </c>
       <c r="X6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y6" t="n">
         <v>4.7</v>
@@ -1458,16 +1525,16 @@
         <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1485,16 +1552,16 @@
         <v>23</v>
       </c>
       <c r="AJ6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK6" t="n">
         <v>27</v>
       </c>
       <c r="AL6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN6" t="n">
         <v>15</v>
@@ -1503,7 +1570,7 @@
         <v>21</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ6" t="n">
         <v>28</v>
@@ -1515,7 +1582,7 @@
         <v>12</v>
       </c>
       <c r="AT6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU6" t="n">
         <v>24</v>
@@ -1539,7 +1606,7 @@
         <v>23</v>
       </c>
       <c r="BB6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC6" t="n">
         <v>16</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>4.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>9</v>
@@ -1661,7 +1728,7 @@
         <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
@@ -1670,7 +1737,7 @@
         <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL7" t="n">
         <v>20</v>
@@ -1682,7 +1749,7 @@
         <v>21</v>
       </c>
       <c r="AO7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP7" t="n">
         <v>13</v>
@@ -1694,7 +1761,7 @@
         <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
         <v>6</v>
@@ -1721,7 +1788,7 @@
         <v>14</v>
       </c>
       <c r="BB7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
         <v>9</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1843,7 +1910,7 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1876,7 +1943,7 @@
         <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT8" t="n">
         <v>5</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E9" t="n">
         <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>0.705</v>
+        <v>0.714</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
@@ -1956,13 +2023,13 @@
         <v>79.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L9" t="n">
         <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="N9" t="n">
         <v>0.368</v>
@@ -1971,16 +2038,16 @@
         <v>18.5</v>
       </c>
       <c r="P9" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="R9" t="n">
         <v>11.9</v>
       </c>
       <c r="S9" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T9" t="n">
         <v>41.2</v>
@@ -1995,10 +2062,10 @@
         <v>7.2</v>
       </c>
       <c r="X9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z9" t="n">
         <v>20.6</v>
@@ -2007,13 +2074,13 @@
         <v>19.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2037,10 +2104,10 @@
         <v>13</v>
       </c>
       <c r="AL9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN9" t="n">
         <v>12</v>
@@ -2052,7 +2119,7 @@
         <v>20</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR9" t="n">
         <v>11</v>
@@ -2088,7 +2155,7 @@
         <v>17</v>
       </c>
       <c r="BC9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>2.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
@@ -2207,7 +2274,7 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL10" t="n">
         <v>2</v>
@@ -2228,7 +2295,7 @@
         <v>22</v>
       </c>
       <c r="AO10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP10" t="n">
         <v>15</v>
@@ -2249,7 +2316,7 @@
         <v>10</v>
       </c>
       <c r="AV10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW10" t="n">
         <v>2</v>
@@ -2264,7 +2331,7 @@
         <v>27</v>
       </c>
       <c r="BA10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -2299,43 +2366,43 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
         <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>0.679</v>
+        <v>0.675</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
       </c>
       <c r="I11" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J11" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L11" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="O11" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P11" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q11" t="n">
         <v>0.727</v>
@@ -2344,7 +2411,7 @@
         <v>12.2</v>
       </c>
       <c r="S11" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T11" t="n">
         <v>44.6</v>
@@ -2368,25 +2435,25 @@
         <v>19.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AD11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF11" t="n">
         <v>5</v>
       </c>
-      <c r="AE11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>4</v>
-      </c>
       <c r="AG11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
         <v>25</v>
@@ -2401,7 +2468,7 @@
         <v>19</v>
       </c>
       <c r="AL11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM11" t="n">
         <v>7</v>
@@ -2422,10 +2489,10 @@
         <v>8</v>
       </c>
       <c r="AS11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
         <v>14</v>
@@ -2434,13 +2501,13 @@
         <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX11" t="n">
         <v>7</v>
       </c>
       <c r="AY11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ11" t="n">
         <v>3</v>
@@ -2449,10 +2516,10 @@
         <v>27</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
@@ -2571,7 +2638,7 @@
         <v>20</v>
       </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
         <v>9</v>
@@ -2595,10 +2662,10 @@
         <v>12</v>
       </c>
       <c r="AP12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR12" t="n">
         <v>17</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2753,13 +2820,13 @@
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
@@ -2807,7 +2874,7 @@
         <v>15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -2923,19 +2990,19 @@
         <v>6.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>4</v>
       </c>
       <c r="AF14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
@@ -2962,7 +3029,7 @@
         <v>5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
         <v>19</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,13 +3184,13 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AI15" t="n">
         <v>10</v>
       </c>
       <c r="AJ15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK15" t="n">
         <v>14</v>
@@ -3135,10 +3202,10 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP15" t="n">
         <v>14</v>
@@ -3153,7 +3220,7 @@
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU15" t="n">
         <v>29</v>
@@ -3174,10 +3241,10 @@
         <v>4</v>
       </c>
       <c r="BA15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC15" t="n">
         <v>24</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-8.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI16" t="n">
         <v>30</v>
@@ -3314,7 +3381,7 @@
         <v>22</v>
       </c>
       <c r="AM16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN16" t="n">
         <v>18</v>
@@ -3326,7 +3393,7 @@
         <v>23</v>
       </c>
       <c r="AQ16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
@@ -3344,7 +3411,7 @@
         <v>22</v>
       </c>
       <c r="AW16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX16" t="n">
         <v>22</v>
@@ -3356,13 +3423,13 @@
         <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB16" t="n">
         <v>30</v>
       </c>
       <c r="BC16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E17" t="n">
         <v>26</v>
       </c>
       <c r="F17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G17" t="n">
-        <v>0.333</v>
+        <v>0.338</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
@@ -3418,22 +3485,22 @@
         <v>5.5</v>
       </c>
       <c r="M17" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.342</v>
+        <v>0.34</v>
       </c>
       <c r="O17" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P17" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q17" t="n">
         <v>0.736</v>
       </c>
       <c r="R17" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="S17" t="n">
         <v>28.8</v>
@@ -3448,7 +3515,7 @@
         <v>14.7</v>
       </c>
       <c r="W17" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X17" t="n">
         <v>4.5</v>
@@ -3463,13 +3530,13 @@
         <v>21</v>
       </c>
       <c r="AB17" t="n">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.6</v>
+        <v>-6.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
@@ -3490,7 +3557,7 @@
         <v>10</v>
       </c>
       <c r="AK17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
         <v>24</v>
@@ -3508,7 +3575,7 @@
         <v>21</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR17" t="n">
         <v>4</v>
@@ -3523,7 +3590,7 @@
         <v>17</v>
       </c>
       <c r="AV17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW17" t="n">
         <v>21</v>
@@ -3532,19 +3599,19 @@
         <v>20</v>
       </c>
       <c r="AY17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ17" t="n">
         <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>22</v>
       </c>
       <c r="BC17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E18" t="n">
         <v>19</v>
       </c>
       <c r="F18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G18" t="n">
-        <v>0.244</v>
+        <v>0.247</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
@@ -3591,28 +3658,28 @@
         <v>37.3</v>
       </c>
       <c r="J18" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L18" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M18" t="n">
         <v>15.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.345</v>
+        <v>0.342</v>
       </c>
       <c r="O18" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="P18" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.737</v>
+        <v>0.736</v>
       </c>
       <c r="R18" t="n">
         <v>11.6</v>
@@ -3621,7 +3688,7 @@
         <v>29.4</v>
       </c>
       <c r="T18" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U18" t="n">
         <v>19.9</v>
@@ -3642,16 +3709,16 @@
         <v>23</v>
       </c>
       <c r="AA18" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.2</v>
+        <v>-6.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>28</v>
@@ -3687,10 +3754,10 @@
         <v>30</v>
       </c>
       <c r="AP18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR18" t="n">
         <v>12</v>
@@ -3708,7 +3775,7 @@
         <v>18</v>
       </c>
       <c r="AW18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E19" t="n">
         <v>32</v>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G19" t="n">
-        <v>0.41</v>
+        <v>0.416</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>34.7</v>
+        <v>34.9</v>
       </c>
       <c r="J19" t="n">
         <v>78.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.441</v>
+        <v>0.443</v>
       </c>
       <c r="L19" t="n">
         <v>6</v>
@@ -3785,7 +3852,7 @@
         <v>17.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.348</v>
+        <v>0.347</v>
       </c>
       <c r="O19" t="n">
         <v>20.1</v>
@@ -3794,7 +3861,7 @@
         <v>27.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.734</v>
+        <v>0.732</v>
       </c>
       <c r="R19" t="n">
         <v>11.4</v>
@@ -3806,7 +3873,7 @@
         <v>42.2</v>
       </c>
       <c r="U19" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V19" t="n">
         <v>15</v>
@@ -3827,13 +3894,13 @@
         <v>22.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5</v>
+        <v>-4.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
         <v>21</v>
@@ -3890,7 +3957,7 @@
         <v>25</v>
       </c>
       <c r="AW19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AX19" t="n">
         <v>17</v>
@@ -3899,7 +3966,7 @@
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA19" t="n">
         <v>6</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -3937,31 +4004,31 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E20" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F20" t="n">
         <v>23</v>
       </c>
       <c r="G20" t="n">
-        <v>0.705</v>
+        <v>0.701</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J20" t="n">
         <v>82.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.466</v>
+        <v>0.464</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M20" t="n">
         <v>19.8</v>
@@ -3973,10 +4040,10 @@
         <v>15.9</v>
       </c>
       <c r="P20" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="R20" t="n">
         <v>11.5</v>
@@ -3985,13 +4052,13 @@
         <v>30.4</v>
       </c>
       <c r="T20" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U20" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V20" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="W20" t="n">
         <v>7.7</v>
@@ -4003,28 +4070,28 @@
         <v>4.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA20" t="n">
         <v>19.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.8</v>
+        <v>100.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="n">
         <v>13</v>
@@ -4036,13 +4103,13 @@
         <v>8</v>
       </c>
       <c r="AK20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL20" t="n">
         <v>6</v>
       </c>
       <c r="AM20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN20" t="n">
         <v>3</v>
@@ -4051,10 +4118,10 @@
         <v>29</v>
       </c>
       <c r="AP20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
         <v>14</v>
@@ -4063,7 +4130,7 @@
         <v>15</v>
       </c>
       <c r="AT20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU20" t="n">
         <v>13</v>
@@ -4087,7 +4154,7 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC20" t="n">
         <v>5</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -4119,55 +4186,55 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F21" t="n">
         <v>56</v>
       </c>
       <c r="G21" t="n">
-        <v>0.291</v>
+        <v>0.282</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J21" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L21" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M21" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0.336</v>
+        <v>0.335</v>
       </c>
       <c r="O21" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="P21" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.726</v>
+        <v>0.725</v>
       </c>
       <c r="R21" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S21" t="n">
         <v>29.9</v>
       </c>
       <c r="T21" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="U21" t="n">
         <v>18.6</v>
@@ -4185,22 +4252,22 @@
         <v>5.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>96.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-6.5</v>
+        <v>-6.6</v>
       </c>
       <c r="AD21" t="n">
         <v>1</v>
       </c>
       <c r="AE21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF21" t="n">
         <v>26</v>
@@ -4215,7 +4282,7 @@
         <v>24</v>
       </c>
       <c r="AJ21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AK21" t="n">
         <v>28</v>
@@ -4230,31 +4297,31 @@
         <v>27</v>
       </c>
       <c r="AO21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP21" t="n">
         <v>11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS21" t="n">
         <v>20</v>
       </c>
       <c r="AT21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU21" t="n">
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,16 +4330,16 @@
         <v>24</v>
       </c>
       <c r="AZ21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB21" t="n">
         <v>24</v>
       </c>
       <c r="BC21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E22" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F22" t="n">
         <v>29</v>
       </c>
       <c r="G22" t="n">
-        <v>0.628</v>
+        <v>0.623</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J22" t="n">
-        <v>78.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="K22" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L22" t="n">
         <v>9.699999999999999</v>
@@ -4331,7 +4398,7 @@
         <v>25.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="O22" t="n">
         <v>20.4</v>
@@ -4340,19 +4407,19 @@
         <v>28.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.724</v>
+        <v>0.725</v>
       </c>
       <c r="R22" t="n">
         <v>9.4</v>
       </c>
       <c r="S22" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T22" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="U22" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V22" t="n">
         <v>14.4</v>
@@ -4373,22 +4440,22 @@
         <v>23.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.3</v>
+        <v>104.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AE22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF22" t="n">
         <v>9</v>
       </c>
       <c r="AG22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH22" t="n">
         <v>18</v>
@@ -4397,7 +4464,7 @@
         <v>13</v>
       </c>
       <c r="AJ22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK22" t="n">
         <v>5</v>
@@ -4418,16 +4485,16 @@
         <v>3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR22" t="n">
         <v>28</v>
       </c>
       <c r="AS22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU22" t="n">
         <v>22</v>
@@ -4439,7 +4506,7 @@
         <v>27</v>
       </c>
       <c r="AX22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY22" t="n">
         <v>8</v>
@@ -4454,7 +4521,7 @@
         <v>6</v>
       </c>
       <c r="BC22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E23" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F23" t="n">
         <v>38</v>
       </c>
       <c r="G23" t="n">
-        <v>0.513</v>
+        <v>0.506</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4501,10 +4568,10 @@
         <v>37.2</v>
       </c>
       <c r="J23" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L23" t="n">
         <v>3.6</v>
@@ -4516,7 +4583,7 @@
         <v>0.317</v>
       </c>
       <c r="O23" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P23" t="n">
         <v>26.4</v>
@@ -4525,19 +4592,19 @@
         <v>0.71</v>
       </c>
       <c r="R23" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S23" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T23" t="n">
         <v>41.8</v>
       </c>
       <c r="U23" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V23" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W23" t="n">
         <v>8.6</v>
@@ -4555,13 +4622,13 @@
         <v>21</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="AC23" t="n">
         <v>0.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AE23" t="n">
         <v>15</v>
@@ -4582,7 +4649,7 @@
         <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -4594,16 +4661,16 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP23" t="n">
         <v>10</v>
       </c>
       <c r="AQ23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS23" t="n">
         <v>28</v>
@@ -4624,16 +4691,16 @@
         <v>9</v>
       </c>
       <c r="AY23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ23" t="n">
         <v>7</v>
       </c>
       <c r="BA23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F24" t="n">
         <v>26</v>
       </c>
       <c r="G24" t="n">
-        <v>0.671</v>
+        <v>0.667</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4683,25 +4750,25 @@
         <v>41.5</v>
       </c>
       <c r="J24" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K24" t="n">
-        <v>0.501</v>
+        <v>0.5</v>
       </c>
       <c r="L24" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="M24" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="N24" t="n">
         <v>0.394</v>
       </c>
       <c r="O24" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P24" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Q24" t="n">
         <v>0.785</v>
@@ -4716,10 +4783,10 @@
         <v>41.2</v>
       </c>
       <c r="U24" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="V24" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W24" t="n">
         <v>6.6</v>
@@ -4731,22 +4798,22 @@
         <v>3.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>110.3</v>
+        <v>110.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AD24" t="n">
         <v>1</v>
       </c>
       <c r="AE24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF24" t="n">
         <v>7</v>
@@ -4755,7 +4822,7 @@
         <v>7</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
@@ -4776,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="AO24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP24" t="n">
         <v>22</v>
@@ -4809,7 +4876,7 @@
         <v>2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA24" t="n">
         <v>15</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>-1</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="n">
         <v>16</v>
@@ -4937,7 +5004,7 @@
         <v>16</v>
       </c>
       <c r="AH25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI25" t="n">
         <v>27</v>
@@ -4964,7 +5031,7 @@
         <v>25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR25" t="n">
         <v>18</v>
@@ -4991,7 +5058,7 @@
         <v>1</v>
       </c>
       <c r="AZ25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA25" t="n">
         <v>21</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5119,7 +5186,7 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="n">
         <v>14</v>
@@ -5152,7 +5219,7 @@
         <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
         <v>27</v>
@@ -5167,7 +5234,7 @@
         <v>7</v>
       </c>
       <c r="AX26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY26" t="n">
         <v>27</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E27" t="n">
         <v>53</v>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G27" t="n">
-        <v>0.679</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H27" t="n">
         <v>48.1</v>
@@ -5229,28 +5296,28 @@
         <v>35.7</v>
       </c>
       <c r="J27" t="n">
-        <v>78.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="K27" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L27" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M27" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O27" t="n">
         <v>16.6</v>
       </c>
       <c r="P27" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="R27" t="n">
         <v>9.6</v>
@@ -5259,13 +5326,13 @@
         <v>31.8</v>
       </c>
       <c r="T27" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U27" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V27" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W27" t="n">
         <v>6.3</v>
@@ -5280,16 +5347,16 @@
         <v>18.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB27" t="n">
-        <v>95.3</v>
+        <v>95.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AE27" t="n">
         <v>4</v>
@@ -5316,7 +5383,7 @@
         <v>8</v>
       </c>
       <c r="AM27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN27" t="n">
         <v>11</v>
@@ -5328,16 +5395,16 @@
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR27" t="n">
         <v>26</v>
       </c>
       <c r="AS27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU27" t="n">
         <v>21</v>
@@ -5364,7 +5431,7 @@
         <v>26</v>
       </c>
       <c r="BC27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E28" t="n">
         <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G28" t="n">
-        <v>0.228</v>
+        <v>0.231</v>
       </c>
       <c r="H28" t="n">
         <v>48.4</v>
       </c>
       <c r="I28" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J28" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L28" t="n">
         <v>3.9</v>
@@ -5423,13 +5490,13 @@
         <v>11.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.333</v>
+        <v>0.334</v>
       </c>
       <c r="O28" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P28" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q28" t="n">
         <v>0.77</v>
@@ -5438,16 +5505,16 @@
         <v>11.9</v>
       </c>
       <c r="S28" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T28" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U28" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V28" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W28" t="n">
         <v>6.4</v>
@@ -5456,19 +5523,19 @@
         <v>4.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.5</v>
+        <v>97.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>-8.9</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AD28" t="n">
         <v>1</v>
@@ -5483,7 +5550,7 @@
         <v>29</v>
       </c>
       <c r="AH28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
@@ -5510,16 +5577,16 @@
         <v>24</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
         <v>10</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AT28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU28" t="n">
         <v>15</v>
@@ -5546,7 +5613,7 @@
         <v>16</v>
       </c>
       <c r="BC28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -5575,34 +5642,34 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E29" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F29" t="n">
         <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5</v>
+        <v>0.494</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J29" t="n">
         <v>82</v>
       </c>
       <c r="K29" t="n">
-        <v>0.469</v>
+        <v>0.468</v>
       </c>
       <c r="L29" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M29" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="N29" t="n">
         <v>0.394</v>
@@ -5626,10 +5693,10 @@
         <v>40.1</v>
       </c>
       <c r="U29" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V29" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="W29" t="n">
         <v>6.9</v>
@@ -5647,22 +5714,22 @@
         <v>18.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.4</v>
+        <v>100.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AE29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF29" t="n">
         <v>16</v>
       </c>
       <c r="AG29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH29" t="n">
         <v>8</v>
@@ -5677,7 +5744,7 @@
         <v>7</v>
       </c>
       <c r="AL29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM29" t="n">
         <v>14</v>
@@ -5695,7 +5762,7 @@
         <v>1</v>
       </c>
       <c r="AR29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS29" t="n">
         <v>14</v>
@@ -5725,7 +5792,7 @@
         <v>29</v>
       </c>
       <c r="BB29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -5835,19 +5902,19 @@
         <v>7.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF30" t="n">
         <v>7</v>
       </c>
       <c r="AG30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI30" t="n">
         <v>4</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5880,7 +5947,7 @@
         <v>13</v>
       </c>
       <c r="AS30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT30" t="n">
         <v>24</v>
@@ -5910,7 +5977,7 @@
         <v>5</v>
       </c>
       <c r="BC30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
@@ -5939,46 +6006,46 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E31" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F31" t="n">
         <v>37</v>
       </c>
       <c r="G31" t="n">
-        <v>0.526</v>
+        <v>0.519</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J31" t="n">
         <v>81.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L31" t="n">
         <v>6.9</v>
       </c>
       <c r="M31" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N31" t="n">
         <v>0.353</v>
       </c>
       <c r="O31" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="P31" t="n">
         <v>24.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.787</v>
+        <v>0.788</v>
       </c>
       <c r="R31" t="n">
         <v>12.1</v>
@@ -5987,19 +6054,19 @@
         <v>29.3</v>
       </c>
       <c r="T31" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U31" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="V31" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W31" t="n">
         <v>7.8</v>
       </c>
       <c r="X31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y31" t="n">
         <v>4.4</v>
@@ -6008,16 +6075,16 @@
         <v>19.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6038,16 +6105,16 @@
         <v>16</v>
       </c>
       <c r="AK31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AN31" t="n">
         <v>20</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>19</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
@@ -6065,19 +6132,19 @@
         <v>26</v>
       </c>
       <c r="AT31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU31" t="n">
         <v>27</v>
       </c>
       <c r="AV31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW31" t="n">
         <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY31" t="n">
         <v>9</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-9-2007-08</t>
+          <t>2008-04-09</t>
         </is>
       </c>
     </row>
